--- a/data/evaluation_results_3.xlsx
+++ b/data/evaluation_results_3.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prompts'!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Metadata'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -439,11 +439,10 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +478,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ttft_seconds</t>
+          <t>total_latency_seconds</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>total_latency_seconds</t>
+          <t>input_tokens</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>input_tokens</t>
+          <t>output_tokens</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>output_tokens</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -517,10 +511,56 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a non-uniform, what is the most likely consequence for the student?</t>
+          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a uniform that is not approved by the school administration, what is the most likely consequence for the student?</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Based on the given priorities, I would prioritize the following requirements:
+1. Safety and policy compliance
+2. Factual correctness
+3. Explicit user requirements
+4. Relevance
+5. Brevity
+Considering these priorities, the most likely consequence for the student would be:
+The student is likely to receive a warning or detention for violating the school's uniform policy, which is intended to ensure safety and maintain a professional learning environment.
+This consequence is relevant to the situation, as it addresses the policy violation and maintains the safety and order of the classroom. It also aligns with the explicit user requirement of following school policies.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:31:46.277062+00:00</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1.288138516000345</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a uniform that is not approved by the school administration, what is the most likely consequence for the student?</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Based on the given priorities, I would prioritize the requirements as follows:
 1. Safety and policy compliance
@@ -528,54 +568,51 @@
 3. Explicit user requirements
 4. Relevance
 5. Brevity
-Considering these priorities, the most likely consequence for the student would be:
-The student would likely receive a warning or a verbal reminder about the school's uniform policy.
+Given these priorities, the most likely consequence for the student would be:
+The student would likely receive a warning or detention for violating the school's uniform policy.
 This consequence is most likely because:
-* Safety and policy compliance are top priorities, and wearing a non-uniform may be seen as a breach of school rules.
-* Factual correctness is not directly relevant to the consequence, as the student's intention is not being questioned.
-* Explicit user requirements are not explicitly stated, but the consequence is likely to be a warning or reminder, which is a common consequence for violating school policies.
-* Relevance is not a priority in this scenario, as the consequence is not being determined based on the student's actions or behavior.
-* Brevity is not a priority, as the consequence is not being determined to be brief or concise.
-It's worth noting that the specific consequence may vary depending on the school's policies and the student's behavior. However, based on the given priorities, a warning or verbal reminder is the most likely consequence.</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T17:59:40.057353+00:00</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>2.151747840000098</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>2.182815608000055</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>116</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>252</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+* Safety and policy compliance are top priorities, and wearing an unauthorized uniform may pose a distraction or disruption to the learning environment.
+* The student's action is a clear violation of the school's policy, which is a factual requirement.
+* The explicit user requirement is that the student is aware of and follows the school's uniform policy.
+* The consequence is relevant to the situation, as it addresses the student's non-compliance with the policy.
+* The consequence is brief and straightforward, as a warning or detention is a common and effective disciplinary action.
+Note that the specific consequence may vary depending on the school's policies and procedures, but a warning or detention is a likely outcome.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:31:47.565561+00:00</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>2.001414335999925</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a non-uniform, what is the most likely consequence for the student?</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a uniform that is not approved by the school administration, what is the most likely consequence for the student?</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Based on the given priorities, I would prioritize the requirements as follows:
 1. Safety and policy compliance
@@ -583,90 +620,32 @@
 3. Explicit user requirements
 4. Relevance
 5. Brevity
-Considering these priorities, the most likely consequence for the student would be:
-The student would likely receive a warning or a verbal reminder about the school's uniform policy.
+Given these priorities, the most likely consequence for the student would be:
+The student is likely to receive a warning or detention for violating the school's uniform policy.
 This consequence is most likely because:
-* Safety and policy compliance are top priorities, and wearing a non-uniform may be seen as a breach of school rules.
-* Factual correctness is not directly relevant to the consequence, as the student's actions are already known to be non-compliant.
-* Explicit user requirements are not explicitly stated, but the consequence is likely to be a warning or reminder, which is a common consequence for non-compliance with school policies.
-* Relevance is not a priority in this case, as the consequence is likely to be a standard response to a known infraction.
-* Brevity is not a priority, as the consequence is likely to be a brief warning or reminder.
-Note that the specific consequence may vary depending on the school's policies and the student's age and behavior.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T17:59:42.240641+00:00</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>2.133318250999992</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>2.163728226999865</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>116</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>239</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a non-uniform, what is the most likely consequence for the student?</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Based on the given priorities, I would prioritize the requirements as follows:
-1. Safety and policy compliance
-2. Factual correctness
-3. Explicit user requirements
-4. Relevance
-5. Brevity
-Considering these priorities, the most likely consequence for the student would be:
-The student would likely receive a warning or a verbal reminder about the school's uniform policy.
-This consequence is most likely because:
-* Safety and policy compliance are top priorities, and wearing a non-uniform may be seen as a breach of school rules.
-* Factual correctness is not directly relevant to the consequence, as the student's actions are already known to be non-compliant.
-* Explicit user requirements are not explicitly stated in the question, but the consequence is likely to be a warning or reminder, which is a common consequence for non-compliance with school policies.
-* Relevance is not a priority in this case, as the consequence is likely to be a standard response to a non-compliant action.
-* Brevity is not a priority, as the consequence may need to be explained to the student.
-It's worth noting that the specific consequence may vary depending on the school's policies and the student's age and behavior.</t>
+* Safety and policy compliance are top priorities, and wearing an unauthorized uniform may pose a distraction or disruption to the learning environment.
+* Factual correctness is not directly relevant to the consequence, as the student's actions are already known to be unauthorized.
+* Explicit user requirements are met, as the student is aware of the school's uniform policy and is violating it.
+* Relevance is high, as the student's actions have a direct impact on the school's policies and the learning environment.
+* Brevity is not a concern, as the consequence is straightforward and clear.
+Note that the specific consequence may vary depending on the school's policies and the student's prior behavior.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:59:44.404783+00:00</t>
+          <t>2026-10-22T04:31:49.567428+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2.164039468000055</v>
+        <v>1.972489237000445</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>2.195557315000087</v>
+        <v>122</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>116</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>245</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+        <v>218</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -686,6 +665,102 @@
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>To solve this problem, let's use algebra. 
+Let's say the cost of the ball is x. Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
+The total cost of the bat and the ball together is $1.10, so we can set up the equation:
+x + (x + $1.00) = $1.10
+Combine like terms:
+2x + $1.00 = $1.10
+Subtract $1.00 from both sides:
+2x = $0.10
+Divide both sides by 2:
+x = $0.05
+So, the ball costs $0.05.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:31:51.540305+00:00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>1.41992045500001</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>A bat and a ball together cost $1.10. The bat costs $1.00 more than the ball. How much does the ball cost?</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>To solve this problem, let's use algebra. 
+Let's say the cost of the ball is x dollars. Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
+The total cost of the bat and the ball together is $1.10, so we can set up the equation:
+x + (x + $1.00) = $1.10
+Combine like terms:
+2x + $1.00 = $1.10
+Subtract $1.00 from both sides:
+2x = $0.10
+Divide both sides by 2:
+x = $0.05
+So, the ball costs $0.05.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:31:52.960461+00:00</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1.447871374999977</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>A bat and a ball together cost $1.10. The bat costs $1.00 more than the ball. How much does the ball cost?</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>To solve this problem, let's break it down step by step.
 Let's say the cost of the ball is x.
@@ -701,123 +776,21 @@
 So, the ball costs $0.05.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T17:59:46.600632+00:00</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>1.440801577999991</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>1.457223080000176</v>
-      </c>
-      <c r="I5" s="2" t="n">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:31:54.408556+00:00</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>1.461458580999988</v>
+      </c>
+      <c r="H7" s="2" t="n">
         <v>113</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="I7" s="2" t="n">
         <v>152</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>A bat and a ball together cost $1.10. The bat costs $1.00 more than the ball. How much does the ball cost?</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>To solve this problem, let's use algebra. 
-Let's say the cost of the ball is x dollars. Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
-The total cost of the bat and the ball together is $1.10, so we can set up the equation:
-x + (x + $1.00) = $1.10
-Combine like terms:
-2x + $1.00 = $1.10
-Subtract $1.00 from both sides:
-2x = $0.10
-Divide both sides by 2:
-x = $0.05
-So, the ball costs $0.05.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T17:59:48.058113+00:00</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>1.433579910000162</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>1.457000471000129</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>A bat and a ball together cost $1.10. The bat costs $1.00 more than the ball. How much does the ball cost?</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>To solve this problem, let's break it down step by step:
-1. Let's denote the cost of the ball as x.
-2. Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
-3. The total cost of the bat and the ball together is $1.10, so we can set up the equation: x + (x + $1.00) = $1.10.
-4. Simplify the equation: 2x + $1.00 = $1.10.
-5. Subtract $1.00 from both sides: 2x = $0.10.
-6. Divide both sides by 2: x = $0.05.
-Therefore, the ball costs $0.05.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T17:59:49.515361+00:00</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>1.444440442000086</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>1.463235119000046</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>165</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -839,32 +812,29 @@
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>To solve this problem, let's break it down step by step.
-The snail climbs 3 feet up during the day and slips back 2 feet at night, so it effectively moves 1 foot up each day. 
+The snail climbs 3 feet up during the day and slips back 2 feet at night, so it effectively moves 1 foot up the well each day.
 Since the well is 20 feet deep, the snail needs to cover 20 feet. 
-To find the number of days it takes for the snail to reach the top, we can divide the total depth of the well by the effective daily progress:
-20 feet (total depth) / 1 foot (effective daily progress) = 20 days
+To find the number of days it takes for the snail to reach the top, we can divide the total depth of the well (20 feet) by the effective daily progress (1 foot).
+20 feet / 1 foot per day = 20 days
 However, on the 20th day, the snail will climb 3 feet and reach the top of the well, but it won't slip back because it's already at the top. 
-So, the correct answer is 20 days, but the snail will reach the top on the 20th day, not on the 19th day.</t>
+So, the correct answer is 20 days.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:59:50.978852+00:00</t>
+          <t>2026-10-22T04:31:55.870357+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1.699984137000001</v>
+        <v>1.59136973700015</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1.721166939000113</v>
+        <v>135</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>135</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>192</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+        <v>170</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -886,32 +856,34 @@
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>To solve this problem, let's break it down step by step.
-The snail climbs 3 feet up during the day and slips back 2 feet at night, so it effectively moves 1 foot up each day. 
-However, on the final day, the snail will climb 3 feet and reach the top of the well without slipping back. 
-So, we need to calculate the number of days it takes for the snail to climb 18 feet (since 20 - 2 = 18, considering the 2-foot slip at night).
-18 feet / 1 foot per day = 18 days
-On the 19th day, the snail climbs 3 feet and reaches the top of the well. 
-Therefore, it will take the snail 19 days to reach the top of the well.</t>
+The snail climbs 3 feet up during the day and slips back 2 feet at night, resulting in a net gain of 1 foot per day.
+Since the well is 20 feet deep, we need to find out how many days it will take for the snail to cover 20 feet.
+Let's calculate the number of days:
+Day 1: 3 feet (up) - 2 feet (down) = 1 foot net gain
+Day 2: 3 feet (up) - 2 feet (down) = 1 foot net gain (total: 2 feet)
+Day 3: 3 feet (up) - 2 feet (down) = 1 foot net gain (total: 3 feet)
+...
+Day 19: 3 feet (up) - 2 feet (down) = 1 foot net gain (total: 19 feet)
+Day 20: 3 feet (up) - 2 feet (down) = 1 foot net gain (total: 20 feet)
+On the 20th day, the snail will reach the top of the well.
+Therefore, it will take the snail 20 days to reach the top of the 20-foot well.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:59:52.700245+00:00</t>
+          <t>2026-10-22T04:31:57.462054+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1.591643459000124</v>
+        <v>2.405989713999588</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1.61362457600012</v>
+        <v>135</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>135</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>170</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+        <v>270</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -932,40 +904,33 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>To solve this problem, we need to consider the net progress of the snail each day.
-The snail climbs 3 feet up during the day, but slips back 2 feet at night, resulting in a net progress of 1 foot per day.
-Since the well is 20 feet deep, the snail needs to make a net progress of 20 feet to reach the top.
-To find the number of days required, we can divide the total depth of the well by the net progress of the snail per day:
-20 feet (total depth) ÷ 1 foot (net progress per day) = 20 days
-However, this calculation assumes that the snail will climb 3 feet and slip back 2 feet every day, without considering the final day when the snail will reach the top.
-On the 20th day, the snail will climb 3 feet and reach the top of the well, but it won't slip back 2 feet because it will be at the top. Therefore, the correct answer is 20 days, but we need to verify this by checking the progress on the 20th day.
-On the 20th day, the snail will climb 3 feet and reach the top, so it won't slip back 2 feet. The correct calculation is:
-Day 1-19: 19 days of net progress of 1 foot per day, resulting in a total progress of 19 feet.
-Day 20: The snail climbs 3 feet and reaches the top, so it won't slip back 2 feet.
-The final answer is 20 days.</t>
+          <t>To solve this problem, let's break it down step by step.
+The snail climbs 3 feet up during the day and slips back 2 feet at night, so it effectively moves 1 foot up each day. 
+Since the well is 20 feet deep, the snail needs to cover 20 feet. 
+To find the number of days it takes for the snail to reach the top, we can divide the total depth of the well (20 feet) by the effective daily progress (1 foot).
+20 feet / 1 foot per day = 20 days
+However, on the 20th day, the snail will climb 3 feet and reach the top of the well, but it won't slip back 2 feet because it's already at the top. 
+So, the snail will reach the top of the well on the 20th day.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:59:54.314086+00:00</t>
+          <t>2026-10-22T04:31:59.868313+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2.786308823999889</v>
+        <v>1.679837162999775</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2.815723098000035</v>
+        <v>135</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>135</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>332</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+        <v>181</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:J10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1001,7 +966,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a non-uniform, what is the most likely consequence for the student?</t>
+          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a uniform that is not approved by the school administration, what is the most likely consequence for the student?</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1065,10 +1030,12 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>{
-  "median_ttft": 1.591643459,
-  "median_latency": 1.613624576,
-  "correct_frequency": 0.8333333333333334,
-  "misinformation_frequency": 0
+  "median_input": 119,
+  "median_output": 184,
+  "median_latency": 1.697,
+  "correct_frequency": 0.75,
+  "misinformation_frequency": 0,
+  "relevance_frequency": 1
 }</t>
         </is>
       </c>
@@ -1076,45 +1043,65 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>median_ttft</t>
+          <t>median_input</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.591643459</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>median_latency</t>
+          <t>median_output</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.613624576</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>correct_frequency</t>
+          <t>median_latency</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.697</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>correct_frequency</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>misinformation_frequency</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>relevance_frequency</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1152,7 +1139,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:59:58.602006+00:00</t>
+          <t>2026-10-22T04:32:02.982780+00:00</t>
         </is>
       </c>
     </row>
